--- a/교재/엑셀교재v2/015-017_수학삼각함수_실습.xlsx
+++ b/교재/엑셀교재v2/015-017_수학삼각함수_실습.xlsx
@@ -323,7 +323,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -381,6 +381,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -728,7 +737,7 @@
       </c>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" spans="1:10" ht="27.95" customHeight="1">
+    <row r="6" spans="1:10" ht="44" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
         <v>7</v>
@@ -746,8 +755,11 @@
         <v>50</v>
       </c>
       <c r="G6" s="1"/>
-      <c r="H6" s="4" t="s">
-        <v>17</v>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">판매총액
+(SUMPRODUCT 함수 사용)</t>
+        </is>
       </c>
       <c r="I6" s="5"/>
       <c r="J6" s="1"/>
@@ -1024,10 +1036,12 @@
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
     </row>
-    <row r="18" spans="1:10" ht="27.95" customHeight="1">
+    <row r="18" spans="1:10" ht="44" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="19" t="s">
-        <v>42</v>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">판매수량 합계 (SUM 함수 사용)</t>
+        </is>
       </c>
       <c r="C18" s="19"/>
       <c r="D18" s="19"/>
@@ -1040,10 +1054,12 @@
       <c r="I18" s="9"/>
       <c r="J18" s="1"/>
     </row>
-    <row r="19" spans="1:10" ht="27.95" customHeight="1">
+    <row r="19" spans="1:10" ht="44" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="19" t="s">
-        <v>44</v>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">판매금액 평균 (AVERAGE 함수 사용)</t>
+        </is>
       </c>
       <c r="C19" s="19"/>
       <c r="D19" s="19"/>
@@ -1054,10 +1070,12 @@
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
     </row>
-    <row r="20" spans="1:10" ht="27.95" customHeight="1">
+    <row r="20" spans="1:10" ht="44" customHeight="1">
       <c r="A20" s="1"/>
-      <c r="B20" s="19" t="s">
-        <v>45</v>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서초점 판매금액 합계 (SUMIF 함수 사용)</t>
+        </is>
       </c>
       <c r="C20" s="19"/>
       <c r="D20" s="19"/>
@@ -1070,10 +1088,12 @@
       <c r="I20" s="20"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="1:10" ht="27.95" customHeight="1">
+    <row r="21" spans="1:10" ht="44" customHeight="1">
       <c r="A21" s="1"/>
-      <c r="B21" s="19" t="s">
-        <v>47</v>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">강남점 판매수량 평균 (AVERAGEIF 함수 사용)</t>
+        </is>
       </c>
       <c r="C21" s="19"/>
       <c r="D21" s="19"/>
@@ -1084,10 +1104,12 @@
       <c r="I21" s="20"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="1:10" ht="27.95" customHeight="1">
+    <row r="22" spans="1:10" ht="44" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="19" t="s">
-        <v>48</v>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서초점이며 TV인 판매수량 합계 (SUMIFS 함수 사용)</t>
+        </is>
       </c>
       <c r="C22" s="19"/>
       <c r="D22" s="19"/>
@@ -1098,10 +1120,12 @@
       <c r="I22" s="20"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="1:10" ht="27.95" customHeight="1">
+    <row r="23" spans="1:10" ht="44" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="19" t="s">
-        <v>49</v>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구로점이며 에어컨인 판매금액 평균 (AVERAGEIFS 함수 사용)</t>
+        </is>
       </c>
       <c r="C23" s="19"/>
       <c r="D23" s="19"/>
@@ -1112,10 +1136,12 @@
       <c r="I23" s="20"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="1:10" ht="27.95" customHeight="1">
+    <row r="24" spans="1:10" ht="44" customHeight="1">
       <c r="A24" s="1"/>
-      <c r="B24" s="19" t="s">
-        <v>50</v>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">판매수량 중앙값 (MEDIAN 함수 사용)</t>
+        </is>
       </c>
       <c r="C24" s="19"/>
       <c r="D24" s="19"/>
@@ -1373,7 +1399,7 @@
       </c>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" spans="1:10" ht="27.95" customHeight="1">
+    <row r="6" spans="1:10" ht="44" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
         <v>7</v>
@@ -1391,8 +1417,11 @@
         <v>50</v>
       </c>
       <c r="G6" s="1"/>
-      <c r="H6" s="4" t="s">
-        <v>17</v>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">판매총액
+(SUMPRODUCT 함수 사용)</t>
+        </is>
       </c>
       <c r="I6" s="10">
         <f>SUMPRODUCT(H3:H5,I3:I5)</f>
@@ -1690,10 +1719,12 @@
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
     </row>
-    <row r="18" spans="1:10" ht="27.95" customHeight="1">
+    <row r="18" spans="1:10" ht="44" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="19" t="s">
-        <v>42</v>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">판매수량 합계 (SUM 함수 사용)</t>
+        </is>
       </c>
       <c r="C18" s="19"/>
       <c r="D18" s="19"/>
@@ -1712,10 +1743,12 @@
       </c>
       <c r="J18" s="1"/>
     </row>
-    <row r="19" spans="1:10" ht="27.95" customHeight="1">
+    <row r="19" spans="1:10" ht="44" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="19" t="s">
-        <v>44</v>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">판매금액 평균 (AVERAGE 함수 사용)</t>
+        </is>
       </c>
       <c r="C19" s="19"/>
       <c r="D19" s="19"/>
@@ -1729,10 +1762,12 @@
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
     </row>
-    <row r="20" spans="1:10" ht="27.95" customHeight="1">
+    <row r="20" spans="1:10" ht="44" customHeight="1">
       <c r="A20" s="1"/>
-      <c r="B20" s="19" t="s">
-        <v>45</v>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서초점 판매금액 합계 (SUMIF 함수 사용)</t>
+        </is>
       </c>
       <c r="C20" s="19"/>
       <c r="D20" s="19"/>
@@ -1748,10 +1783,12 @@
       <c r="I20" s="20"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="1:10" ht="27.95" customHeight="1">
+    <row r="21" spans="1:10" ht="44" customHeight="1">
       <c r="A21" s="1"/>
-      <c r="B21" s="19" t="s">
-        <v>47</v>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">강남점 판매수량 평균 (AVERAGEIF 함수 사용)</t>
+        </is>
       </c>
       <c r="C21" s="19"/>
       <c r="D21" s="19"/>
@@ -1765,10 +1802,12 @@
       <c r="I21" s="20"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="1:10" ht="27.95" customHeight="1">
+    <row r="22" spans="1:10" ht="44" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="19" t="s">
-        <v>48</v>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서초점이며 TV인 판매수량 합계 (SUMIFS 함수 사용)</t>
+        </is>
       </c>
       <c r="C22" s="19"/>
       <c r="D22" s="19"/>
@@ -1782,10 +1821,12 @@
       <c r="I22" s="20"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="1:10" ht="27.95" customHeight="1">
+    <row r="23" spans="1:10" ht="44" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="19" t="s">
-        <v>49</v>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구로점이며 에어컨인 판매금액 평균 (AVERAGEIFS 함수 사용)</t>
+        </is>
       </c>
       <c r="C23" s="19"/>
       <c r="D23" s="19"/>
@@ -1799,10 +1840,12 @@
       <c r="I23" s="20"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="1:10" ht="27.95" customHeight="1">
+    <row r="24" spans="1:10" ht="44" customHeight="1">
       <c r="A24" s="1"/>
-      <c r="B24" s="19" t="s">
-        <v>50</v>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">판매수량 중앙값 (MEDIAN 함수 사용)</t>
+        </is>
       </c>
       <c r="C24" s="19"/>
       <c r="D24" s="19"/>
@@ -1990,7 +2033,7 @@
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="1:10" ht="27.95" customHeight="1">
+    <row r="4" spans="1:10" ht="44" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="1" t="s">
         <v>28</v>
@@ -2002,15 +2045,18 @@
         <v>1</v>
       </c>
       <c r="E4" s="15"/>
-      <c r="F4" s="1" t="s">
-        <v>56</v>
+      <c r="F4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">소수 첫째 자리까지 반올림
+(ROUND 함수 사용)</t>
+        </is>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" spans="1:10" ht="27.95" customHeight="1">
+    <row r="5" spans="1:10" ht="44" customHeight="1">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
         <v>28</v>
@@ -2022,15 +2068,18 @@
         <v>-2</v>
       </c>
       <c r="E5" s="9"/>
-      <c r="F5" s="1" t="s">
-        <v>57</v>
+      <c r="F5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">백의 자리까지 반올림
+(ROUND 함수 사용)</t>
+        </is>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" spans="1:10" ht="27.95" customHeight="1">
+    <row r="6" spans="1:10" ht="44" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
         <v>32</v>
@@ -2042,15 +2091,18 @@
         <v>0</v>
       </c>
       <c r="E6" s="9"/>
-      <c r="F6" s="1" t="s">
-        <v>58</v>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">음수를 정수 자리까지 올림
+(ROUNDUP 함수 사용)</t>
+        </is>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
     </row>
-    <row r="7" spans="1:10" ht="27.95" customHeight="1">
+    <row r="7" spans="1:10" ht="44" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
         <v>30</v>
@@ -2062,15 +2114,18 @@
         <v>0</v>
       </c>
       <c r="E7" s="9"/>
-      <c r="F7" s="1" t="s">
-        <v>59</v>
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">음수를 정수 자리까지 내림
+(ROUNDDOWN 함수 사용)</t>
+        </is>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="1:10" ht="27.95" customHeight="1">
+    <row r="8" spans="1:10" ht="44" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
         <v>34</v>
@@ -2082,15 +2137,18 @@
         <v>0</v>
       </c>
       <c r="E8" s="9"/>
-      <c r="F8" s="1" t="s">
-        <v>60</v>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">음수의 소수 부분 자름
+(TRUNC 함수 사용)</t>
+        </is>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
     </row>
-    <row r="9" spans="1:10" ht="27.95" customHeight="1">
+    <row r="9" spans="1:10" ht="44" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="1" t="s">
         <v>36</v>
@@ -2100,15 +2158,18 @@
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="9"/>
-      <c r="F9" s="1" t="s">
-        <v>61</v>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">원본보다 크지 않은 정수
+(INT 함수 사용)</t>
+        </is>
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
     </row>
-    <row r="10" spans="1:10" ht="27.95" customHeight="1">
+    <row r="10" spans="1:10" ht="44" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1" t="s">
         <v>32</v>
@@ -2120,15 +2181,18 @@
         <v>-1</v>
       </c>
       <c r="E10" s="9"/>
-      <c r="F10" s="1" t="s">
-        <v>62</v>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이미 십의 자리인 값 올림
+(ROUNDUP 함수 사용)</t>
+        </is>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
     </row>
-    <row r="11" spans="1:10" ht="27.95" customHeight="1">
+    <row r="11" spans="1:10" ht="44" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1" t="s">
         <v>34</v>
@@ -2140,8 +2204,11 @@
         <v>-2</v>
       </c>
       <c r="E11" s="9"/>
-      <c r="F11" s="1" t="s">
-        <v>63</v>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">십의 자리에서 자름
+(TRUNC 함수 사용)</t>
+        </is>
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
@@ -2471,7 +2538,7 @@
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="1:10" ht="27.95" customHeight="1">
+    <row r="4" spans="1:10" ht="44" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="1" t="s">
         <v>28</v>
@@ -2486,15 +2553,18 @@
         <f>ROUND(C4,D4)</f>
         <v>9876.5</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>56</v>
+      <c r="F4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">소수 첫째 자리까지 반올림
+(ROUND 함수 사용)</t>
+        </is>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" spans="1:10" ht="27.95" customHeight="1">
+    <row r="5" spans="1:10" ht="44" customHeight="1">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
         <v>28</v>
@@ -2509,15 +2579,18 @@
         <f>ROUND(C5,D5)</f>
         <v>9900</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>57</v>
+      <c r="F5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">백의 자리까지 반올림
+(ROUND 함수 사용)</t>
+        </is>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" spans="1:10" ht="27.95" customHeight="1">
+    <row r="6" spans="1:10" ht="44" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
         <v>32</v>
@@ -2532,15 +2605,18 @@
         <f>ROUNDUP(C6,D6)</f>
         <v>-6</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>58</v>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">음수를 정수 자리까지 올림
+(ROUNDUP 함수 사용)</t>
+        </is>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
     </row>
-    <row r="7" spans="1:10" ht="27.95" customHeight="1">
+    <row r="7" spans="1:10" ht="44" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
         <v>30</v>
@@ -2555,15 +2631,18 @@
         <f>ROUNDDOWN(C7,D7)</f>
         <v>-5</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>59</v>
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">음수를 정수 자리까지 내림
+(ROUNDDOWN 함수 사용)</t>
+        </is>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="1:10" ht="27.95" customHeight="1">
+    <row r="8" spans="1:10" ht="44" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
         <v>34</v>
@@ -2578,15 +2657,18 @@
         <f>TRUNC(C8,D8)</f>
         <v>-5</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>60</v>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">음수의 소수 부분 자름
+(TRUNC 함수 사용)</t>
+        </is>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
     </row>
-    <row r="9" spans="1:10" ht="27.95" customHeight="1">
+    <row r="9" spans="1:10" ht="44" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="1" t="s">
         <v>36</v>
@@ -2599,15 +2681,18 @@
         <f>INT(C9)</f>
         <v>-6</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>61</v>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">원본보다 크지 않은 정수
+(INT 함수 사용)</t>
+        </is>
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
     </row>
-    <row r="10" spans="1:10" ht="27.95" customHeight="1">
+    <row r="10" spans="1:10" ht="44" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1" t="s">
         <v>32</v>
@@ -2622,15 +2707,18 @@
         <f>ROUNDUP(C10,D10)</f>
         <v>12340</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>62</v>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이미 십의 자리인 값 올림
+(ROUNDUP 함수 사용)</t>
+        </is>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
     </row>
-    <row r="11" spans="1:10" ht="27.95" customHeight="1">
+    <row r="11" spans="1:10" ht="44" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1" t="s">
         <v>34</v>
@@ -2645,8 +2733,11 @@
         <f>TRUNC(C11,D11)</f>
         <v>12300</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>63</v>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">십의 자리에서 자름
+(TRUNC 함수 사용)</t>
+        </is>
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
